--- a/artfynd/A 17785-2024 artfynd.xlsx
+++ b/artfynd/A 17785-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -900,32 +900,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65736325</v>
+        <v>128729203</v>
       </c>
       <c r="B4" t="n">
-        <v>57942</v>
+        <v>57323</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>102119</v>
+        <v>100112</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Göktyta</t>
+          <t>Ljungpipare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jynx torquilla</t>
+          <t>Pluvialis apricaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -933,11 +933,9 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -976,22 +974,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2017-05-22</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>08:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2017-05-22</t>
+          <t>2025-09-27</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,10 +1016,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66428658</v>
+        <v>65736325</v>
       </c>
       <c r="B5" t="n">
-        <v>58195</v>
+        <v>57942</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1029,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>102122</v>
+        <v>102119</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Flodsångare</t>
+          <t>Göktyta</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Locustella fluviatilis</t>
+          <t>Jynx torquilla</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Wolf, 1810)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1094,22 +1092,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>00:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-06-27</t>
+          <t>2017-05-22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>05:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,37 +1134,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>53586621</v>
+        <v>66428658</v>
       </c>
       <c r="B6" t="n">
-        <v>57774</v>
+        <v>58195</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>102976</v>
+        <v>102122</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Flodsångare</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Locustella fluviatilis</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Wolf, 1810)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1212,22 +1210,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2015-05-23</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>00:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2015-05-23</t>
+          <t>2017-06-27</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,42 +1252,46 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>64802196</v>
+        <v>53586621</v>
       </c>
       <c r="B7" t="n">
-        <v>58541</v>
+        <v>57774</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102987</v>
+        <v>102976</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sädesärla</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Motacilla alba</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hagalund 6,Ytternäs, Upl</t>
@@ -1326,22 +1328,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2017-04-06</t>
+          <t>2015-05-23</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2017-04-06</t>
+          <t>2015-05-23</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,32 +1370,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>64802128</v>
+        <v>64802196</v>
       </c>
       <c r="B8" t="n">
-        <v>58449</v>
+        <v>58541</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102993</v>
+        <v>102987</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svart rödstjärt</t>
+          <t>Sädesärla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phoenicurus ochruros</t>
+          <t>Motacilla alba</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(S.G. Gmelin, 1774)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1402,11 +1404,7 @@
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>honfärgad</t>
-        </is>
-      </c>
+      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1444,12 +1442,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2017-04-05</t>
+          <t>2017-04-06</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2017-04-05</t>
+          <t>2017-04-06</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1476,10 +1484,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125815431</v>
+        <v>64802128</v>
       </c>
       <c r="B9" t="n">
-        <v>58198</v>
+        <v>58449</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1487,21 +1495,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103003</v>
+        <v>102993</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gräshoppsångare</t>
+          <t>Svart rödstjärt</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Locustella naevia</t>
+          <t>Phoenicurus ochruros</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Boddaert, 1783)</t>
+          <t>(S.G. Gmelin, 1774)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1509,34 +1517,26 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>honfärgad</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Hagalund 6, Upl</t>
+          <t>Hagalund 6,Ytternäs, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>702272</v>
+        <v>702255</v>
       </c>
       <c r="R9" t="n">
-        <v>6649242</v>
+        <v>6649248</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1560,22 +1560,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>21:50</t>
+          <t>2017-04-05</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-06-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>21:50</t>
+          <t>2017-04-05</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1602,32 +1592,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>60155839</v>
+        <v>125815431</v>
       </c>
       <c r="B10" t="n">
-        <v>58439</v>
+        <v>58198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103018</v>
+        <v>103003</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Gräshoppsångare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Locustella naevia</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Boddaert, 1783)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1640,25 +1630,29 @@
           <t>adult</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>föda åt ungar</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Hagalund 6,Ytternäs, Upl</t>
+          <t>Hagalund 6, Upl</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>702255</v>
+        <v>702272</v>
       </c>
       <c r="R10" t="n">
-        <v>6649248</v>
+        <v>6649242</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1682,22 +1676,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2016-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2016-06-15</t>
+          <t>2025-06-08</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1724,32 +1718,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>64802273</v>
+        <v>60155839</v>
       </c>
       <c r="B11" t="n">
-        <v>58353</v>
+        <v>58439</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103037</v>
+        <v>103018</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Stare</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sturnus vulgaris</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1757,11 +1751,15 @@
           <t>1</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
-          <t>bobygge</t>
+          <t>föda åt ungar</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1800,22 +1798,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2017-04-06</t>
+          <t>2016-06-15</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2017-04-06</t>
+          <t>2016-06-15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:30</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1839,6 +1837,124 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>64802273</v>
+      </c>
+      <c r="B12" t="n">
+        <v>58353</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>103037</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Stare</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sturnus vulgaris</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>bobygge</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Hagalund 6,Ytternäs, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>702255</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6649248</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ununge</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2017-04-06</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2017-04-06</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Tomas Larsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 17785-2024 artfynd.xlsx
+++ b/artfynd/A 17785-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128729159</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -897,6 +907,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53665294</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1013,6 +1028,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128729203</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1131,6 +1151,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65736325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66428658</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/53586621</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64802196</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1589,6 +1629,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64802128</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1715,6 +1760,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125815431</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1837,6 +1887,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/60155839</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1955,8 +2010,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/64802273</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>